--- a/00_hotspot/results/hotspot_summary.xlsx
+++ b/00_hotspot/results/hotspot_summary.xlsx
@@ -12,13 +12,16 @@
     <sheet name="법정동별" sheetId="3" r:id="rId3"/>
     <sheet name="반복지번_Top30" sheetId="4" r:id="rId4"/>
     <sheet name="월별" sheetId="5" r:id="rId5"/>
+    <sheet name="주차구역공백_자치구" sheetId="6" r:id="rId6"/>
+    <sheet name="주차구역공백_동구간" sheetId="7" r:id="rId7"/>
+    <sheet name="주차구역0곳_동" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="220">
   <si>
     <t>값</t>
   </si>
@@ -53,7 +56,13 @@
     <t>주차구역 수(전체)</t>
   </si>
   <si>
-    <t>주차구역 중 동 이름을 읽은 곳</t>
+    <t>주차구역 중 법정동 배정(지번 주소)</t>
+  </si>
+  <si>
+    <t>주차구역 중 법정동 배정(도로명 주소 조회)</t>
+  </si>
+  <si>
+    <t>주차구역 0곳 동에서 난 점자블록 견인 비중</t>
   </si>
   <si>
     <t>전체견인</t>
@@ -645,6 +654,33 @@
   </si>
   <si>
     <t>월</t>
+  </si>
+  <si>
+    <t>점자블록견인_비중</t>
+  </si>
+  <si>
+    <t>주차구역_비중</t>
+  </si>
+  <si>
+    <t>비중차(견인-주차)</t>
+  </si>
+  <si>
+    <t>주차구역1곳당_점자블록견인</t>
+  </si>
+  <si>
+    <t>동수</t>
+  </si>
+  <si>
+    <t>견인비중</t>
+  </si>
+  <si>
+    <t>0곳</t>
+  </si>
+  <si>
+    <t>1–2곳</t>
+  </si>
+  <si>
+    <t>3곳 이상</t>
   </si>
 </sst>
 </file>
@@ -1006,7 +1042,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1099,7 +1135,23 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>209</v>
+        <v>230</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>0.3943661971830986</v>
       </c>
     </row>
   </sheetData>
@@ -1114,27 +1166,27 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B2">
         <v>4944</v>
@@ -1154,7 +1206,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B3">
         <v>3171</v>
@@ -1174,7 +1226,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B4">
         <v>5224</v>
@@ -1194,7 +1246,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B5">
         <v>4899</v>
@@ -1214,7 +1266,7 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B6">
         <v>6030</v>
@@ -1234,7 +1286,7 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B7">
         <v>6842</v>
@@ -1254,7 +1306,7 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B8">
         <v>1897</v>
@@ -1274,7 +1326,7 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B9">
         <v>1987</v>
@@ -1294,7 +1346,7 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B10">
         <v>1979</v>
@@ -1314,7 +1366,7 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B11">
         <v>1686</v>
@@ -1334,7 +1386,7 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B12">
         <v>2831</v>
@@ -1354,7 +1406,7 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B13">
         <v>2718</v>
@@ -1374,7 +1426,7 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B14">
         <v>3391</v>
@@ -1394,7 +1446,7 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B15">
         <v>1007</v>
@@ -1414,7 +1466,7 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B16">
         <v>1961</v>
@@ -1434,7 +1486,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B17">
         <v>89</v>
@@ -1454,7 +1506,7 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B18">
         <v>339</v>
@@ -1474,7 +1526,7 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B19">
         <v>379</v>
@@ -1494,7 +1546,7 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B20">
         <v>10</v>
@@ -1514,7 +1566,7 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B21">
         <v>13305</v>
@@ -1534,7 +1586,7 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B22">
         <v>14</v>
@@ -1554,7 +1606,7 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B23">
         <v>8</v>
@@ -1574,7 +1626,7 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -1594,7 +1646,7 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -1611,7 +1663,7 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -1638,27 +1690,27 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C2">
         <v>113</v>
@@ -1672,10 +1724,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C3">
         <v>85</v>
@@ -1684,15 +1736,15 @@
         <v>2646</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C4">
         <v>61</v>
@@ -1706,10 +1758,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C5">
         <v>52</v>
@@ -1723,10 +1775,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C6">
         <v>50</v>
@@ -1740,10 +1792,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C7">
         <v>46</v>
@@ -1752,15 +1804,15 @@
         <v>2419</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C8">
         <v>43</v>
@@ -1769,15 +1821,15 @@
         <v>797</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C9">
         <v>43</v>
@@ -1786,15 +1838,15 @@
         <v>3440</v>
       </c>
       <c r="E9">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C10">
         <v>42</v>
@@ -1808,10 +1860,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C11">
         <v>40</v>
@@ -1825,10 +1877,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C12">
         <v>40</v>
@@ -1837,15 +1889,15 @@
         <v>1539</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C13">
         <v>36</v>
@@ -1859,10 +1911,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C14">
         <v>36</v>
@@ -1876,10 +1928,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C15">
         <v>36</v>
@@ -1893,10 +1945,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B16" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C16">
         <v>35</v>
@@ -1910,10 +1962,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C17">
         <v>30</v>
@@ -1922,15 +1974,15 @@
         <v>800</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C18">
         <v>28</v>
@@ -1944,10 +1996,10 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C19">
         <v>28</v>
@@ -1961,10 +2013,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B20" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C20">
         <v>27</v>
@@ -1973,15 +2025,15 @@
         <v>1579</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C21">
         <v>23</v>
@@ -1995,10 +2047,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B22" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C22">
         <v>23</v>
@@ -2007,15 +2059,15 @@
         <v>656</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C23">
         <v>21</v>
@@ -2029,10 +2081,10 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C24">
         <v>20</v>
@@ -2046,10 +2098,10 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C25">
         <v>17</v>
@@ -2058,15 +2110,15 @@
         <v>830</v>
       </c>
       <c r="E25">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B26" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C26">
         <v>17</v>
@@ -2080,10 +2132,10 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C27">
         <v>16</v>
@@ -2097,10 +2149,10 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C28">
         <v>15</v>
@@ -2114,10 +2166,10 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B29" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C29">
         <v>15</v>
@@ -2126,15 +2178,15 @@
         <v>514</v>
       </c>
       <c r="E29">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B30" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C30">
         <v>13</v>
@@ -2143,15 +2195,15 @@
         <v>470</v>
       </c>
       <c r="E30">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B31" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C31">
         <v>12</v>
@@ -2160,15 +2212,15 @@
         <v>1157</v>
       </c>
       <c r="E31">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B32" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C32">
         <v>12</v>
@@ -2182,10 +2234,10 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B33" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C33">
         <v>11</v>
@@ -2199,10 +2251,10 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B34" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C34">
         <v>11</v>
@@ -2211,15 +2263,15 @@
         <v>1144</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B35" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C35">
         <v>11</v>
@@ -2233,10 +2285,10 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C36">
         <v>10</v>
@@ -2250,10 +2302,10 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B37" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C37">
         <v>10</v>
@@ -2267,10 +2319,10 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B38" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C38">
         <v>10</v>
@@ -2284,10 +2336,10 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B39" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C39">
         <v>9</v>
@@ -2301,10 +2353,10 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B40" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C40">
         <v>9</v>
@@ -2318,10 +2370,10 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C41">
         <v>9</v>
@@ -2335,10 +2387,10 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B42" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C42">
         <v>8</v>
@@ -2352,10 +2404,10 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B43" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C43">
         <v>8</v>
@@ -2369,10 +2421,10 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B44" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C44">
         <v>8</v>
@@ -2386,10 +2438,10 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B45" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C45">
         <v>8</v>
@@ -2398,15 +2450,15 @@
         <v>196</v>
       </c>
       <c r="E45">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B46" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C46">
         <v>8</v>
@@ -2420,10 +2472,10 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B47" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C47">
         <v>8</v>
@@ -2437,10 +2489,10 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B48" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C48">
         <v>7</v>
@@ -2454,10 +2506,10 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B49" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C49">
         <v>7</v>
@@ -2471,10 +2523,10 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B50" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C50">
         <v>7</v>
@@ -2483,15 +2535,15 @@
         <v>504</v>
       </c>
       <c r="E50">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B51" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C51">
         <v>7</v>
@@ -2505,10 +2557,10 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B52" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C52">
         <v>7</v>
@@ -2522,10 +2574,10 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C53">
         <v>7</v>
@@ -2534,15 +2586,15 @@
         <v>394</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B54" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C54">
         <v>6</v>
@@ -2556,10 +2608,10 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B55" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C55">
         <v>6</v>
@@ -2573,10 +2625,10 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B56" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C56">
         <v>6</v>
@@ -2590,10 +2642,10 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B57" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C57">
         <v>6</v>
@@ -2607,10 +2659,10 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B58" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C58">
         <v>6</v>
@@ -2619,15 +2671,15 @@
         <v>162</v>
       </c>
       <c r="E58">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B59" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C59">
         <v>6</v>
@@ -2641,10 +2693,10 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B60" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C60">
         <v>5</v>
@@ -2653,15 +2705,15 @@
         <v>265</v>
       </c>
       <c r="E60">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B61" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C61">
         <v>5</v>
@@ -2675,10 +2727,10 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B62" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C62">
         <v>5</v>
@@ -2687,15 +2739,15 @@
         <v>356</v>
       </c>
       <c r="E62">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B63" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C63">
         <v>5</v>
@@ -2704,15 +2756,15 @@
         <v>231</v>
       </c>
       <c r="E63">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B64" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C64">
         <v>5</v>
@@ -2726,10 +2778,10 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B65" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C65">
         <v>4</v>
@@ -2743,10 +2795,10 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B66" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C66">
         <v>4</v>
@@ -2760,10 +2812,10 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B67" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C67">
         <v>4</v>
@@ -2777,10 +2829,10 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B68" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C68">
         <v>4</v>
@@ -2794,10 +2846,10 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B69" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C69">
         <v>3</v>
@@ -2811,10 +2863,10 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B70" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C70">
         <v>3</v>
@@ -2828,10 +2880,10 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B71" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C71">
         <v>3</v>
@@ -2845,10 +2897,10 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B72" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C72">
         <v>3</v>
@@ -2862,10 +2914,10 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B73" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C73">
         <v>3</v>
@@ -2879,10 +2931,10 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B74" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C74">
         <v>3</v>
@@ -2896,10 +2948,10 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B75" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C75">
         <v>3</v>
@@ -2913,10 +2965,10 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B76" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C76">
         <v>3</v>
@@ -2930,10 +2982,10 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B77" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C77">
         <v>3</v>
@@ -2947,10 +2999,10 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B78" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C78">
         <v>3</v>
@@ -2964,10 +3016,10 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B79" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C79">
         <v>3</v>
@@ -2981,10 +3033,10 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B80" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C80">
         <v>3</v>
@@ -2998,10 +3050,10 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B81" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C81">
         <v>3</v>
@@ -3015,10 +3067,10 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B82" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C82">
         <v>2</v>
@@ -3032,10 +3084,10 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B83" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C83">
         <v>2</v>
@@ -3049,10 +3101,10 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B84" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C84">
         <v>2</v>
@@ -3061,15 +3113,15 @@
         <v>127</v>
       </c>
       <c r="E84">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B85" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C85">
         <v>2</v>
@@ -3083,10 +3135,10 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B86" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C86">
         <v>2</v>
@@ -3100,10 +3152,10 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B87" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C87">
         <v>2</v>
@@ -3117,10 +3169,10 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B88" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C88">
         <v>2</v>
@@ -3134,10 +3186,10 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B89" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C89">
         <v>2</v>
@@ -3151,10 +3203,10 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B90" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C90">
         <v>2</v>
@@ -3168,10 +3220,10 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B91" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C91">
         <v>2</v>
@@ -3185,10 +3237,10 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B92" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C92">
         <v>2</v>
@@ -3202,10 +3254,10 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B93" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C93">
         <v>2</v>
@@ -3219,10 +3271,10 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B94" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C94">
         <v>1</v>
@@ -3236,10 +3288,10 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B95" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C95">
         <v>1</v>
@@ -3253,10 +3305,10 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B96" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C96">
         <v>1</v>
@@ -3270,10 +3322,10 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B97" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C97">
         <v>1</v>
@@ -3282,15 +3334,15 @@
         <v>24</v>
       </c>
       <c r="E97">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B98" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -3304,10 +3356,10 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B99" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C99">
         <v>1</v>
@@ -3321,10 +3373,10 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B100" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C100">
         <v>1</v>
@@ -3333,15 +3385,15 @@
         <v>109</v>
       </c>
       <c r="E100">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B101" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C101">
         <v>1</v>
@@ -3355,10 +3407,10 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B102" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C102">
         <v>1</v>
@@ -3372,10 +3424,10 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B103" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C103">
         <v>1</v>
@@ -3389,10 +3441,10 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B104" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C104">
         <v>1</v>
@@ -3406,10 +3458,10 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B105" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C105">
         <v>1</v>
@@ -3423,10 +3475,10 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B106" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C106">
         <v>1</v>
@@ -3440,10 +3492,10 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B107" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C107">
         <v>1</v>
@@ -3457,10 +3509,10 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B108" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C108">
         <v>1</v>
@@ -3474,10 +3526,10 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B109" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C109">
         <v>1</v>
@@ -3491,10 +3543,10 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B110" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C110">
         <v>1</v>
@@ -3508,10 +3560,10 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B111" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C111">
         <v>1</v>
@@ -3525,10 +3577,10 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B112" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C112">
         <v>1</v>
@@ -3542,10 +3594,10 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B113" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C113">
         <v>1</v>
@@ -3559,10 +3611,10 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B114" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C114">
         <v>1</v>
@@ -3576,10 +3628,10 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B115" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C115">
         <v>1</v>
@@ -3593,10 +3645,10 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B116" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C116">
         <v>1</v>
@@ -3610,10 +3662,10 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B117" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C117">
         <v>1</v>
@@ -3627,10 +3679,10 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B118" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C118">
         <v>1</v>
@@ -3654,78 +3706,78 @@
   <sheetData>
     <row r="1" spans="1:21">
       <c r="A1" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>175</v>
-      </c>
       <c r="U1" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="2" spans="1:21">
       <c r="A2" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D2">
         <v>13</v>
@@ -3784,13 +3836,13 @@
     </row>
     <row r="3" spans="1:21">
       <c r="A3" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D3">
         <v>12</v>
@@ -3849,13 +3901,13 @@
     </row>
     <row r="4" spans="1:21">
       <c r="A4" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D4">
         <v>11</v>
@@ -3914,13 +3966,13 @@
     </row>
     <row r="5" spans="1:21">
       <c r="A5" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D5">
         <v>9</v>
@@ -3979,13 +4031,13 @@
     </row>
     <row r="6" spans="1:21">
       <c r="A6" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D6">
         <v>8</v>
@@ -4044,13 +4096,13 @@
     </row>
     <row r="7" spans="1:21">
       <c r="A7" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D7">
         <v>7</v>
@@ -4109,13 +4161,13 @@
     </row>
     <row r="8" spans="1:21">
       <c r="A8" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -4174,13 +4226,13 @@
     </row>
     <row r="9" spans="1:21">
       <c r="A9" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D9">
         <v>7</v>
@@ -4239,13 +4291,13 @@
     </row>
     <row r="10" spans="1:21">
       <c r="A10" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D10">
         <v>7</v>
@@ -4304,13 +4356,13 @@
     </row>
     <row r="11" spans="1:21">
       <c r="A11" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D11">
         <v>7</v>
@@ -4369,13 +4421,13 @@
     </row>
     <row r="12" spans="1:21">
       <c r="A12" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D12">
         <v>7</v>
@@ -4434,13 +4486,13 @@
     </row>
     <row r="13" spans="1:21">
       <c r="A13" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D13">
         <v>6</v>
@@ -4499,13 +4551,13 @@
     </row>
     <row r="14" spans="1:21">
       <c r="A14" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D14">
         <v>6</v>
@@ -4564,13 +4616,13 @@
     </row>
     <row r="15" spans="1:21">
       <c r="A15" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D15">
         <v>6</v>
@@ -4629,13 +4681,13 @@
     </row>
     <row r="16" spans="1:21">
       <c r="A16" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D16">
         <v>6</v>
@@ -4694,13 +4746,13 @@
     </row>
     <row r="17" spans="1:21">
       <c r="A17" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D17">
         <v>6</v>
@@ -4759,13 +4811,13 @@
     </row>
     <row r="18" spans="1:21">
       <c r="A18" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B18" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C18" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D18">
         <v>5</v>
@@ -4824,13 +4876,13 @@
     </row>
     <row r="19" spans="1:21">
       <c r="A19" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B19" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D19">
         <v>5</v>
@@ -4889,13 +4941,13 @@
     </row>
     <row r="20" spans="1:21">
       <c r="A20" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B20" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C20" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D20">
         <v>5</v>
@@ -4954,13 +5006,13 @@
     </row>
     <row r="21" spans="1:21">
       <c r="A21" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B21" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C21" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D21">
         <v>5</v>
@@ -5019,13 +5071,13 @@
     </row>
     <row r="22" spans="1:21">
       <c r="A22" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B22" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C22" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D22">
         <v>5</v>
@@ -5084,13 +5136,13 @@
     </row>
     <row r="23" spans="1:21">
       <c r="A23" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B23" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C23" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D23">
         <v>5</v>
@@ -5149,13 +5201,13 @@
     </row>
     <row r="24" spans="1:21">
       <c r="A24" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B24" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C24" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D24">
         <v>5</v>
@@ -5214,13 +5266,13 @@
     </row>
     <row r="25" spans="1:21">
       <c r="A25" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B25" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C25" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D25">
         <v>5</v>
@@ -5279,13 +5331,13 @@
     </row>
     <row r="26" spans="1:21">
       <c r="A26" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B26" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C26" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D26">
         <v>5</v>
@@ -5344,13 +5396,13 @@
     </row>
     <row r="27" spans="1:21">
       <c r="A27" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B27" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C27" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D27">
         <v>5</v>
@@ -5409,13 +5461,13 @@
     </row>
     <row r="28" spans="1:21">
       <c r="A28" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B28" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C28" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D28">
         <v>5</v>
@@ -5474,13 +5526,13 @@
     </row>
     <row r="29" spans="1:21">
       <c r="A29" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B29" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C29" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D29">
         <v>5</v>
@@ -5539,13 +5591,13 @@
     </row>
     <row r="30" spans="1:21">
       <c r="A30" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B30" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C30" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D30">
         <v>5</v>
@@ -5604,13 +5656,13 @@
     </row>
     <row r="31" spans="1:21">
       <c r="A31" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B31" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C31" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D31">
         <v>4</v>
@@ -5679,16 +5731,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -5857,6 +5909,1819 @@
       </c>
       <c r="D13">
         <v>0.01661197703035275</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J19"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2">
+        <v>3171</v>
+      </c>
+      <c r="C2">
+        <v>192</v>
+      </c>
+      <c r="D2">
+        <v>0.06054872280037843</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>0.1364605543710021</v>
+      </c>
+      <c r="H2">
+        <v>0.01079136690647482</v>
+      </c>
+      <c r="I2">
+        <v>0.1256691874645273</v>
+      </c>
+      <c r="J2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3">
+        <v>4944</v>
+      </c>
+      <c r="C3">
+        <v>198</v>
+      </c>
+      <c r="D3">
+        <v>0.04004854368932039</v>
+      </c>
+      <c r="E3">
+        <v>5</v>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>0.1407249466950959</v>
+      </c>
+      <c r="H3">
+        <v>0.01798561151079137</v>
+      </c>
+      <c r="I3">
+        <v>0.1227393351843046</v>
+      </c>
+      <c r="J3">
+        <v>39.6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4">
+        <v>1987</v>
+      </c>
+      <c r="C4">
+        <v>91</v>
+      </c>
+      <c r="D4">
+        <v>0.04579768495218923</v>
+      </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>0.06467661691542288</v>
+      </c>
+      <c r="H4">
+        <v>0.01798561151079137</v>
+      </c>
+      <c r="I4">
+        <v>0.04669100540463152</v>
+      </c>
+      <c r="J4">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5">
+        <v>1686</v>
+      </c>
+      <c r="C5">
+        <v>71</v>
+      </c>
+      <c r="D5">
+        <v>0.04211150652431792</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>0.05046197583511016</v>
+      </c>
+      <c r="H5">
+        <v>0.01079136690647482</v>
+      </c>
+      <c r="I5">
+        <v>0.03967060892863534</v>
+      </c>
+      <c r="J5">
+        <v>23.66666666666667</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6">
+        <v>2831</v>
+      </c>
+      <c r="C6">
+        <v>62</v>
+      </c>
+      <c r="D6">
+        <v>0.02190038855528082</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>0.04406538734896944</v>
+      </c>
+      <c r="H6">
+        <v>0.007194244604316547</v>
+      </c>
+      <c r="I6">
+        <v>0.03687114274465289</v>
+      </c>
+      <c r="J6">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7">
+        <v>2718</v>
+      </c>
+      <c r="C7">
+        <v>58</v>
+      </c>
+      <c r="D7">
+        <v>0.0213392200147167</v>
+      </c>
+      <c r="E7">
+        <v>4</v>
+      </c>
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>0.0412224591329069</v>
+      </c>
+      <c r="H7">
+        <v>0.01438848920863309</v>
+      </c>
+      <c r="I7">
+        <v>0.0268339699242738</v>
+      </c>
+      <c r="J7">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8">
+        <v>3391</v>
+      </c>
+      <c r="C8">
+        <v>37</v>
+      </c>
+      <c r="D8">
+        <v>0.01091123562370982</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>0.02629708599857854</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0.02629708599857854</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9">
+        <v>1007</v>
+      </c>
+      <c r="C9">
+        <v>30</v>
+      </c>
+      <c r="D9">
+        <v>0.0297914597815293</v>
+      </c>
+      <c r="E9">
+        <v>3</v>
+      </c>
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>0.02132196162046908</v>
+      </c>
+      <c r="H9">
+        <v>0.01079136690647482</v>
+      </c>
+      <c r="I9">
+        <v>0.01053059471399426</v>
+      </c>
+      <c r="J9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10">
+        <v>1897</v>
+      </c>
+      <c r="C10">
+        <v>102</v>
+      </c>
+      <c r="D10">
+        <v>0.05376910911966262</v>
+      </c>
+      <c r="E10">
+        <v>18</v>
+      </c>
+      <c r="F10" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>0.07249466950959488</v>
+      </c>
+      <c r="H10">
+        <v>0.06474820143884892</v>
+      </c>
+      <c r="I10">
+        <v>0.007746468070745957</v>
+      </c>
+      <c r="J10">
+        <v>5.666666666666667</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11">
+        <v>1961</v>
+      </c>
+      <c r="C11">
+        <v>12</v>
+      </c>
+      <c r="D11">
+        <v>0.006119326874043855</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>0.008528784648187633</v>
+      </c>
+      <c r="H11">
+        <v>0.003597122302158274</v>
+      </c>
+      <c r="I11">
+        <v>0.00493166234602936</v>
+      </c>
+      <c r="J11">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12">
+        <v>6030</v>
+      </c>
+      <c r="C12">
+        <v>108</v>
+      </c>
+      <c r="D12">
+        <v>0.01791044776119403</v>
+      </c>
+      <c r="E12">
+        <v>22</v>
+      </c>
+      <c r="F12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>0.0767590618336887</v>
+      </c>
+      <c r="H12">
+        <v>0.07913669064748201</v>
+      </c>
+      <c r="I12">
+        <v>-0.002377628813793303</v>
+      </c>
+      <c r="J12">
+        <v>4.909090909090909</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13">
+        <v>5224</v>
+      </c>
+      <c r="C13">
+        <v>131</v>
+      </c>
+      <c r="D13">
+        <v>0.02507656967840735</v>
+      </c>
+      <c r="E13">
+        <v>29</v>
+      </c>
+      <c r="F13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>0.09310589907604833</v>
+      </c>
+      <c r="H13">
+        <v>0.1043165467625899</v>
+      </c>
+      <c r="I13">
+        <v>-0.01121064768654161</v>
+      </c>
+      <c r="J13">
+        <v>4.517241379310345</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14">
+        <v>339</v>
+      </c>
+      <c r="C14">
+        <v>4</v>
+      </c>
+      <c r="D14">
+        <v>0.01179941002949852</v>
+      </c>
+      <c r="E14">
+        <v>4</v>
+      </c>
+      <c r="F14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>0.002842928216062544</v>
+      </c>
+      <c r="H14">
+        <v>0.01438848920863309</v>
+      </c>
+      <c r="I14">
+        <v>-0.01154556099257055</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15">
+        <v>379</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15">
+        <v>0.005277044854881266</v>
+      </c>
+      <c r="E15">
+        <v>4</v>
+      </c>
+      <c r="F15" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>0.001421464108031272</v>
+      </c>
+      <c r="H15">
+        <v>0.01438848920863309</v>
+      </c>
+      <c r="I15">
+        <v>-0.01296702510060182</v>
+      </c>
+      <c r="J15">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16">
+        <v>4899</v>
+      </c>
+      <c r="C16">
+        <v>118</v>
+      </c>
+      <c r="D16">
+        <v>0.02408654827515819</v>
+      </c>
+      <c r="E16">
+        <v>28</v>
+      </c>
+      <c r="F16" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>0.08386638237384506</v>
+      </c>
+      <c r="H16">
+        <v>0.1007194244604317</v>
+      </c>
+      <c r="I16">
+        <v>-0.0168530420865866</v>
+      </c>
+      <c r="J16">
+        <v>4.214285714285714</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17">
+        <v>1979</v>
+      </c>
+      <c r="C17">
+        <v>88</v>
+      </c>
+      <c r="D17">
+        <v>0.04446690247599798</v>
+      </c>
+      <c r="E17">
+        <v>39</v>
+      </c>
+      <c r="F17" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>0.06254442075337598</v>
+      </c>
+      <c r="H17">
+        <v>0.1402877697841727</v>
+      </c>
+      <c r="I17">
+        <v>-0.07774334903079667</v>
+      </c>
+      <c r="J17">
+        <v>2.256410256410256</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18">
+        <v>6842</v>
+      </c>
+      <c r="C18">
+        <v>102</v>
+      </c>
+      <c r="D18">
+        <v>0.01490792166033324</v>
+      </c>
+      <c r="E18">
+        <v>49</v>
+      </c>
+      <c r="F18" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>0.07249466950959488</v>
+      </c>
+      <c r="H18">
+        <v>0.1762589928057554</v>
+      </c>
+      <c r="I18">
+        <v>-0.1037643232961605</v>
+      </c>
+      <c r="J18">
+        <v>2.081632653061225</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19">
+        <v>13305</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>7.51597143930853E-05</v>
+      </c>
+      <c r="E19">
+        <v>59</v>
+      </c>
+      <c r="F19" t="b">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>0.0007107320540156361</v>
+      </c>
+      <c r="H19">
+        <v>0.2122302158273381</v>
+      </c>
+      <c r="I19">
+        <v>-0.2115194837733225</v>
+      </c>
+      <c r="J19">
+        <v>0.01694915254237288</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B2">
+        <v>65</v>
+      </c>
+      <c r="C2">
+        <v>560</v>
+      </c>
+      <c r="D2">
+        <v>0.3943661971830986</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B3">
+        <v>29</v>
+      </c>
+      <c r="C3">
+        <v>370</v>
+      </c>
+      <c r="D3">
+        <v>0.2605633802816901</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B4">
+        <v>23</v>
+      </c>
+      <c r="C4">
+        <v>490</v>
+      </c>
+      <c r="D4">
+        <v>0.3450704225352113</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E66"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2">
+        <v>113</v>
+      </c>
+      <c r="D2">
+        <v>2278</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3">
+        <v>36</v>
+      </c>
+      <c r="D3">
+        <v>680</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4">
+        <v>36</v>
+      </c>
+      <c r="D4">
+        <v>497</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5">
+        <v>36</v>
+      </c>
+      <c r="D5">
+        <v>467</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6">
+        <v>35</v>
+      </c>
+      <c r="D6">
+        <v>1586</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7">
+        <v>28</v>
+      </c>
+      <c r="D7">
+        <v>609</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8">
+        <v>28</v>
+      </c>
+      <c r="D8">
+        <v>483</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9">
+        <v>23</v>
+      </c>
+      <c r="D9">
+        <v>483</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10">
+        <v>17</v>
+      </c>
+      <c r="D10">
+        <v>289</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11">
+        <v>16</v>
+      </c>
+      <c r="D11">
+        <v>147</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12">
+        <v>11</v>
+      </c>
+      <c r="D12">
+        <v>389</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" t="s">
+        <v>79</v>
+      </c>
+      <c r="C13">
+        <v>11</v>
+      </c>
+      <c r="D13">
+        <v>106</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14">
+        <v>10</v>
+      </c>
+      <c r="D14">
+        <v>731</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15">
+        <v>9</v>
+      </c>
+      <c r="D15">
+        <v>35</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16">
+        <v>9</v>
+      </c>
+      <c r="D16">
+        <v>901</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17">
+        <v>9</v>
+      </c>
+      <c r="D17">
+        <v>253</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" t="s">
+        <v>86</v>
+      </c>
+      <c r="C18">
+        <v>8</v>
+      </c>
+      <c r="D18">
+        <v>150</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" t="s">
+        <v>88</v>
+      </c>
+      <c r="C19">
+        <v>8</v>
+      </c>
+      <c r="D19">
+        <v>199</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20">
+        <v>8</v>
+      </c>
+      <c r="D20">
+        <v>166</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21">
+        <v>7</v>
+      </c>
+      <c r="D21">
+        <v>144</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22">
+        <v>7</v>
+      </c>
+      <c r="D22">
+        <v>261</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23">
+        <v>7</v>
+      </c>
+      <c r="D23">
+        <v>130</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" t="s">
+        <v>100</v>
+      </c>
+      <c r="C24">
+        <v>6</v>
+      </c>
+      <c r="D24">
+        <v>486</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" t="s">
+        <v>103</v>
+      </c>
+      <c r="C25">
+        <v>6</v>
+      </c>
+      <c r="D25">
+        <v>302</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" t="s">
+        <v>108</v>
+      </c>
+      <c r="C26">
+        <v>5</v>
+      </c>
+      <c r="D26">
+        <v>116</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" t="s">
+        <v>109</v>
+      </c>
+      <c r="C27">
+        <v>4</v>
+      </c>
+      <c r="D27">
+        <v>104</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" t="s">
+        <v>111</v>
+      </c>
+      <c r="C28">
+        <v>4</v>
+      </c>
+      <c r="D28">
+        <v>121</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
+        <v>24</v>
+      </c>
+      <c r="B29" t="s">
+        <v>113</v>
+      </c>
+      <c r="C29">
+        <v>3</v>
+      </c>
+      <c r="D29">
+        <v>215</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" t="s">
+        <v>117</v>
+      </c>
+      <c r="C30">
+        <v>3</v>
+      </c>
+      <c r="D30">
+        <v>286</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31" t="s">
+        <v>118</v>
+      </c>
+      <c r="C31">
+        <v>3</v>
+      </c>
+      <c r="D31">
+        <v>293</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32" t="s">
+        <v>119</v>
+      </c>
+      <c r="C32">
+        <v>3</v>
+      </c>
+      <c r="D32">
+        <v>439</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>120</v>
+      </c>
+      <c r="C33">
+        <v>3</v>
+      </c>
+      <c r="D33">
+        <v>144</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" t="s">
+        <v>121</v>
+      </c>
+      <c r="C34">
+        <v>3</v>
+      </c>
+      <c r="D34">
+        <v>132</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>22</v>
+      </c>
+      <c r="B35" t="s">
+        <v>122</v>
+      </c>
+      <c r="C35">
+        <v>3</v>
+      </c>
+      <c r="D35">
+        <v>148</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" t="s">
+        <v>123</v>
+      </c>
+      <c r="C36">
+        <v>3</v>
+      </c>
+      <c r="D36">
+        <v>221</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
+        <v>24</v>
+      </c>
+      <c r="B37" t="s">
+        <v>125</v>
+      </c>
+      <c r="C37">
+        <v>3</v>
+      </c>
+      <c r="D37">
+        <v>79</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
+        <v>29</v>
+      </c>
+      <c r="B38" t="s">
+        <v>127</v>
+      </c>
+      <c r="C38">
+        <v>2</v>
+      </c>
+      <c r="D38">
+        <v>19</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" t="s">
+        <v>34</v>
+      </c>
+      <c r="B39" t="s">
+        <v>131</v>
+      </c>
+      <c r="C39">
+        <v>2</v>
+      </c>
+      <c r="D39">
+        <v>87</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
+        <v>32</v>
+      </c>
+      <c r="B40" t="s">
+        <v>132</v>
+      </c>
+      <c r="C40">
+        <v>2</v>
+      </c>
+      <c r="D40">
+        <v>60</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" t="s">
+        <v>36</v>
+      </c>
+      <c r="B41" t="s">
+        <v>133</v>
+      </c>
+      <c r="C41">
+        <v>2</v>
+      </c>
+      <c r="D41">
+        <v>31</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" t="s">
+        <v>30</v>
+      </c>
+      <c r="B42" t="s">
+        <v>134</v>
+      </c>
+      <c r="C42">
+        <v>2</v>
+      </c>
+      <c r="D42">
+        <v>66</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" t="s">
+        <v>22</v>
+      </c>
+      <c r="B43" t="s">
+        <v>136</v>
+      </c>
+      <c r="C43">
+        <v>2</v>
+      </c>
+      <c r="D43">
+        <v>302</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" t="s">
+        <v>30</v>
+      </c>
+      <c r="B44" t="s">
+        <v>137</v>
+      </c>
+      <c r="C44">
+        <v>2</v>
+      </c>
+      <c r="D44">
+        <v>140</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" t="s">
+        <v>21</v>
+      </c>
+      <c r="B45" t="s">
+        <v>138</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="D45">
+        <v>27</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" t="s">
+        <v>27</v>
+      </c>
+      <c r="B46" t="s">
+        <v>139</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+      <c r="D46">
+        <v>181</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" t="s">
+        <v>29</v>
+      </c>
+      <c r="B47" t="s">
+        <v>140</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+      <c r="D47">
+        <v>53</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" t="s">
+        <v>33</v>
+      </c>
+      <c r="B48" t="s">
+        <v>142</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+      <c r="D48">
+        <v>85</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" t="s">
+        <v>29</v>
+      </c>
+      <c r="B49" t="s">
+        <v>143</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+      <c r="D49">
+        <v>35</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" t="s">
+        <v>23</v>
+      </c>
+      <c r="B50" t="s">
+        <v>145</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+      <c r="D50">
+        <v>28</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" t="s">
+        <v>23</v>
+      </c>
+      <c r="B51" t="s">
+        <v>146</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
+      </c>
+      <c r="D51">
+        <v>26</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" t="s">
+        <v>22</v>
+      </c>
+      <c r="B52" t="s">
+        <v>147</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+      <c r="D52">
+        <v>53</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" t="s">
+        <v>24</v>
+      </c>
+      <c r="B53" t="s">
+        <v>148</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+      <c r="D53">
+        <v>40</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" t="s">
+        <v>34</v>
+      </c>
+      <c r="B54" t="s">
+        <v>149</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
+      <c r="D54">
+        <v>332</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" t="s">
+        <v>32</v>
+      </c>
+      <c r="B55" t="s">
+        <v>151</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
+      <c r="D55">
+        <v>27</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" t="s">
+        <v>32</v>
+      </c>
+      <c r="B56" t="s">
+        <v>152</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
+      <c r="D56">
+        <v>49</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" t="s">
+        <v>32</v>
+      </c>
+      <c r="B57" t="s">
+        <v>153</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
+      <c r="D57">
+        <v>49</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" t="s">
+        <v>32</v>
+      </c>
+      <c r="B58" t="s">
+        <v>154</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
+      <c r="D58">
+        <v>179</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" t="s">
+        <v>32</v>
+      </c>
+      <c r="B59" t="s">
+        <v>155</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
+      <c r="D59">
+        <v>40</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" t="s">
+        <v>32</v>
+      </c>
+      <c r="B60" t="s">
+        <v>156</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
+      <c r="D60">
+        <v>109</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" t="s">
+        <v>32</v>
+      </c>
+      <c r="B61" t="s">
+        <v>157</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
+      <c r="D61">
+        <v>81</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" t="s">
+        <v>32</v>
+      </c>
+      <c r="B62" t="s">
+        <v>158</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+      <c r="D62">
+        <v>159</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" t="s">
+        <v>36</v>
+      </c>
+      <c r="B63" t="s">
+        <v>159</v>
+      </c>
+      <c r="C63">
+        <v>1</v>
+      </c>
+      <c r="D63">
+        <v>30</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" t="s">
+        <v>36</v>
+      </c>
+      <c r="B64" t="s">
+        <v>160</v>
+      </c>
+      <c r="C64">
+        <v>1</v>
+      </c>
+      <c r="D64">
+        <v>137</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" t="s">
+        <v>37</v>
+      </c>
+      <c r="B65" t="s">
+        <v>161</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
+      <c r="D65">
+        <v>76</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" t="s">
+        <v>37</v>
+      </c>
+      <c r="B66" t="s">
+        <v>162</v>
+      </c>
+      <c r="C66">
+        <v>1</v>
+      </c>
+      <c r="D66">
+        <v>14</v>
+      </c>
+      <c r="E66">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
